--- a/resources/templates/standard/K1200-01.xlsx
+++ b/resources/templates/standard/K1200-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>협력업체 등록대장</t>
   </si>
@@ -768,10 +771,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -810,28 +815,28 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -841,29 +846,29 @@
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="21.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
